--- a/mapping_history.xlsx
+++ b/mapping_history.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -424,13 +424,13 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>0</v>
+        <v>-20.99999921768904</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.104751825332642</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -439,22 +439,22 @@
         <v>0</v>
       </c>
       <c r="F2">
+        <v>0.9799650141074351</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.9799650141074351</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-21.07216092178487</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>1.1025</v>
       </c>
       <c r="L2">
         <v>-0</v>
@@ -462,13 +462,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>-69.37196551263332</v>
+        <v>-108.9999977946281</v>
       </c>
       <c r="B3">
-        <v>2.008064456284046</v>
+        <v>4.999999813735485</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1.104751825332642</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -477,22 +477,22 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.930320258549319</v>
+        <v>0.8958995294206051</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.8958995294206051</v>
       </c>
       <c r="I3">
-        <v>-68.62554112554108</v>
+        <v>-108.6026755199684</v>
       </c>
       <c r="J3">
-        <v>2.018398268397959</v>
+        <v>4.862806366565565</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>1.1025</v>
       </c>
       <c r="L3">
         <v>-0</v>
@@ -500,37 +500,37 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>-153.8248025178909</v>
+        <v>-193.999996483326</v>
       </c>
       <c r="B4">
-        <v>2.008064456284046</v>
+        <v>58.23986707627773</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>1.104414701461792</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0.8455442682451213</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.8067235801368112</v>
       </c>
       <c r="I4">
-        <v>-153.3982683982686</v>
+        <v>-194.5122546626303</v>
       </c>
       <c r="J4">
-        <v>2.018398268397959</v>
+        <v>58.35367639878905</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>1.1025</v>
       </c>
       <c r="L4">
         <v>-0</v>
@@ -538,192 +538,268 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>-159.1553189754486</v>
+        <v>-282.867384078531</v>
       </c>
       <c r="B5">
-        <v>-0.6898125903680921</v>
+        <v>100.3982041408317</v>
       </c>
       <c r="C5">
+        <v>1.104583263397217</v>
+      </c>
+      <c r="D5">
+        <v>-7.741104125976586</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>6.000274658203125</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
       <c r="F5">
-        <v>0.8402040021438003</v>
+        <v>0.910588177553466</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.8121010529628783</v>
       </c>
       <c r="I5">
-        <v>-153.3982683982686</v>
+        <v>-283.663704716336</v>
       </c>
       <c r="J5">
-        <v>2.018398268397959</v>
+        <v>100.4979982423592</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>1.1025</v>
       </c>
       <c r="L5">
-        <v>7.462180129881814</v>
+        <v>-7.780643508251235</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>-157.6902617812157</v>
+        <v>-339.7785731947347</v>
       </c>
       <c r="B6">
-        <v>1.278082033619285</v>
+        <v>150.5964789319393</v>
       </c>
       <c r="C6">
-        <v>1.015432953834534</v>
+        <v>1.104414701461792</v>
       </c>
       <c r="D6">
-        <v>11.5</v>
+        <v>344</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0.8428836286942968</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.8431158312350868</v>
       </c>
       <c r="I6">
-        <v>-153.3982683982686</v>
+        <v>-340.3964456596032</v>
       </c>
       <c r="J6">
-        <v>2.018398268397959</v>
+        <v>150.7469973635389</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>1.1025</v>
       </c>
       <c r="L6">
-        <v>14.98825223028381</v>
+        <v>-16.01141545683459</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>-2.101600653491914</v>
+        <v>-273.5603235040741</v>
       </c>
       <c r="B7">
-        <v>5.153264394029975</v>
+        <v>126.6535739143853</v>
       </c>
       <c r="C7">
-        <v>1.039029836654663</v>
+        <v>1.1044145698053</v>
       </c>
       <c r="D7">
-        <v>23.49786376953125</v>
+        <v>-26.19222259521485</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0.9945192786062109</v>
+        <v>0.9359871749440247</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.9202980537961336</v>
       </c>
       <c r="I7">
-        <v>-153.3982683982686</v>
+        <v>-348.5011229372126</v>
       </c>
       <c r="J7">
-        <v>2.018398268397959</v>
+        <v>191.2703837515869</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>1.1025</v>
       </c>
       <c r="L7">
-        <v>24.47295131167787</v>
+        <v>-24.78342018292236</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>-14.13281655684114</v>
+        <v>-290.4001952360534</v>
       </c>
       <c r="B8">
-        <v>-4.110685860738158</v>
+        <v>180.468713404737</v>
       </c>
       <c r="C8">
-        <v>1.039030313491821</v>
+        <v>1.337622453595856</v>
       </c>
       <c r="D8">
-        <v>19.0023193359375</v>
+        <v>-25.83966064453126</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0.9855052567507037</v>
+        <v>0.9525454376068165</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.9122710950392179</v>
       </c>
       <c r="I8">
-        <v>-10.09199134199139</v>
+        <v>-380.9198320476512</v>
       </c>
       <c r="J8">
-        <v>-6.055194805195015</v>
+        <v>291.7683819939462</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>1.340095640625</v>
       </c>
       <c r="L8">
-        <v>24.47295131167787</v>
+        <v>-24.78342018292236</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>53.34947401285172</v>
+        <v>-310.8183874300259</v>
       </c>
       <c r="B9">
-        <v>181.9083577394485</v>
+        <v>233.39736659391</v>
       </c>
       <c r="C9">
-        <v>1.039031624794006</v>
+        <v>1.388595173465959</v>
       </c>
       <c r="D9">
-        <v>19.02520751953125</v>
+        <v>-111.3044357299805</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>0.8133119585068149</v>
+        <v>0.9293451592183557</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.8798816698632813</v>
       </c>
       <c r="I9">
-        <v>34.31277056277054</v>
+        <v>-426.306024802265</v>
       </c>
       <c r="J9">
-        <v>201.8398268398266</v>
+        <v>401.991992969437</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>1.710339358116314</v>
       </c>
       <c r="L9">
-        <v>24.47295131167787</v>
+        <v>-24.78342018292236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10">
+        <v>-267.8729832210638</v>
+      </c>
+      <c r="B10">
+        <v>111.6959419160419</v>
+      </c>
+      <c r="C10">
+        <v>0.7799681775666798</v>
+      </c>
+      <c r="D10">
+        <v>88.57054901123047</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>0.9128818056176776</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>0.9078565261718416</v>
+      </c>
+      <c r="I10">
+        <v>-463.5875402792692</v>
+      </c>
+      <c r="J10">
+        <v>496.0062493897085</v>
+      </c>
+      <c r="K10">
+        <v>2.292018317801034</v>
+      </c>
+      <c r="L10">
+        <v>-24.78342018292236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>-267.8729832210638</v>
+      </c>
+      <c r="B11">
+        <v>111.6959419160419</v>
+      </c>
+      <c r="C11">
+        <v>0.7799681775666798</v>
+      </c>
+      <c r="D11">
+        <v>88.57054901123047</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>0.9128818056176776</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>0.9078565261718416</v>
+      </c>
+      <c r="I11">
+        <v>-463.5875402792692</v>
+      </c>
+      <c r="J11">
+        <v>496.0062493897085</v>
+      </c>
+      <c r="K11">
+        <v>2.292018317801034</v>
+      </c>
+      <c r="L11">
+        <v>-24.78342018292236</v>
       </c>
     </row>
   </sheetData>

--- a/mapping_history.xlsx
+++ b/mapping_history.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -424,13 +424,13 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>-20.99999921768904</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.104751825332642</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -439,22 +439,22 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9799650141074351</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0.9799650141074351</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>-21.07216092178487</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1.1025</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>-0</v>
@@ -462,344 +462,40 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>-108.9999977946281</v>
+        <v>-140.0000022053719</v>
       </c>
       <c r="B3">
-        <v>4.999999813735485</v>
+        <v>56.00000162422657</v>
       </c>
       <c r="C3">
-        <v>1.104751825332642</v>
+        <v>1.400987982749939</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8958995294206051</v>
+        <v>0.8738934313289796</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0.8958995294206051</v>
+        <v>0.8738934313289796</v>
       </c>
       <c r="I3">
-        <v>-108.6026755199684</v>
+        <v>-140.1298701298701</v>
       </c>
       <c r="J3">
-        <v>4.862806366565565</v>
+        <v>56.59090909090901</v>
       </c>
       <c r="K3">
-        <v>1.1025</v>
+        <v>1.407100422656251</v>
       </c>
       <c r="L3">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>-193.999996483326</v>
-      </c>
-      <c r="B4">
-        <v>58.23986707627773</v>
-      </c>
-      <c r="C4">
-        <v>1.104414701461792</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0.8067235801368112</v>
-      </c>
-      <c r="I4">
-        <v>-194.5122546626303</v>
-      </c>
-      <c r="J4">
-        <v>58.35367639878905</v>
-      </c>
-      <c r="K4">
-        <v>1.1025</v>
-      </c>
-      <c r="L4">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5">
-        <v>-282.867384078531</v>
-      </c>
-      <c r="B5">
-        <v>100.3982041408317</v>
-      </c>
-      <c r="C5">
-        <v>1.104583263397217</v>
-      </c>
-      <c r="D5">
-        <v>-7.741104125976586</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0.910588177553466</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>0.8121010529628783</v>
-      </c>
-      <c r="I5">
-        <v>-283.663704716336</v>
-      </c>
-      <c r="J5">
-        <v>100.4979982423592</v>
-      </c>
-      <c r="K5">
-        <v>1.1025</v>
-      </c>
-      <c r="L5">
-        <v>-7.780643508251235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6">
-        <v>-339.7785731947347</v>
-      </c>
-      <c r="B6">
-        <v>150.5964789319393</v>
-      </c>
-      <c r="C6">
-        <v>1.104414701461792</v>
-      </c>
-      <c r="D6">
-        <v>344</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0.8431158312350868</v>
-      </c>
-      <c r="I6">
-        <v>-340.3964456596032</v>
-      </c>
-      <c r="J6">
-        <v>150.7469973635389</v>
-      </c>
-      <c r="K6">
-        <v>1.1025</v>
-      </c>
-      <c r="L6">
-        <v>-16.01141545683459</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7">
-        <v>-273.5603235040741</v>
-      </c>
-      <c r="B7">
-        <v>126.6535739143853</v>
-      </c>
-      <c r="C7">
-        <v>1.1044145698053</v>
-      </c>
-      <c r="D7">
-        <v>-26.19222259521485</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>0.9359871749440247</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>0.9202980537961336</v>
-      </c>
-      <c r="I7">
-        <v>-348.5011229372126</v>
-      </c>
-      <c r="J7">
-        <v>191.2703837515869</v>
-      </c>
-      <c r="K7">
-        <v>1.1025</v>
-      </c>
-      <c r="L7">
-        <v>-24.78342018292236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8">
-        <v>-290.4001952360534</v>
-      </c>
-      <c r="B8">
-        <v>180.468713404737</v>
-      </c>
-      <c r="C8">
-        <v>1.337622453595856</v>
-      </c>
-      <c r="D8">
-        <v>-25.83966064453126</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>0.9525454376068165</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>0.9122710950392179</v>
-      </c>
-      <c r="I8">
-        <v>-380.9198320476512</v>
-      </c>
-      <c r="J8">
-        <v>291.7683819939462</v>
-      </c>
-      <c r="K8">
-        <v>1.340095640625</v>
-      </c>
-      <c r="L8">
-        <v>-24.78342018292236</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9">
-        <v>-310.8183874300259</v>
-      </c>
-      <c r="B9">
-        <v>233.39736659391</v>
-      </c>
-      <c r="C9">
-        <v>1.388595173465959</v>
-      </c>
-      <c r="D9">
-        <v>-111.3044357299805</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>0.9293451592183557</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>0.8798816698632813</v>
-      </c>
-      <c r="I9">
-        <v>-426.306024802265</v>
-      </c>
-      <c r="J9">
-        <v>401.991992969437</v>
-      </c>
-      <c r="K9">
-        <v>1.710339358116314</v>
-      </c>
-      <c r="L9">
-        <v>-24.78342018292236</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10">
-        <v>-267.8729832210638</v>
-      </c>
-      <c r="B10">
-        <v>111.6959419160419</v>
-      </c>
-      <c r="C10">
-        <v>0.7799681775666798</v>
-      </c>
-      <c r="D10">
-        <v>88.57054901123047</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>0.9128818056176776</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10">
-        <v>0.9078565261718416</v>
-      </c>
-      <c r="I10">
-        <v>-463.5875402792692</v>
-      </c>
-      <c r="J10">
-        <v>496.0062493897085</v>
-      </c>
-      <c r="K10">
-        <v>2.292018317801034</v>
-      </c>
-      <c r="L10">
-        <v>-24.78342018292236</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11">
-        <v>-267.8729832210638</v>
-      </c>
-      <c r="B11">
-        <v>111.6959419160419</v>
-      </c>
-      <c r="C11">
-        <v>0.7799681775666798</v>
-      </c>
-      <c r="D11">
-        <v>88.57054901123047</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>0.9128818056176776</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>0.9078565261718416</v>
-      </c>
-      <c r="I11">
-        <v>-463.5875402792692</v>
-      </c>
-      <c r="J11">
-        <v>496.0062493897085</v>
-      </c>
-      <c r="K11">
-        <v>2.292018317801034</v>
-      </c>
-      <c r="L11">
-        <v>-24.78342018292236</v>
+        <v>19.11348535309122</v>
       </c>
     </row>
   </sheetData>
